--- a/data/trans_orig/IQ26A_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ26A_R2-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12460</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7826</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19185</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15603</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10047</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22196</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10980</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>22404</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>17,55%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12460</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7830</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18095</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36686</t>
+          <t>36278</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72456</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>65731</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>77090</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85,33%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,78%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>73322</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>66729</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>78878</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>66521</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>77945</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>82,45%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,04%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72456</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>66821</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77086</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>85,33%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>137155</t>
+          <t>137563</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152858</t>
+          <t>152721</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>84916</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84916</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>84916</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88925</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88925</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88925</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>84916</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>84916</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>84916</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53386</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42704</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>64589</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>49899</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39226</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>60565</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>39781</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>61800</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>12,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>53386</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>42625</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>64070</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88767</t>
+          <t>90070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118326</t>
+          <t>118320</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>417298</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>406095</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>427980</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>356338</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>345672</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>367011</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>344437</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>366456</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>87,72%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>417298</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>406614</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>428059</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,66%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>758595</t>
+          <t>758601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>788154</t>
+          <t>786851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>470684</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>470684</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>470684</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>406237</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>406237</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>406237</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>470684</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>470684</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>470684</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20280</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14138</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27294</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>25216</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18455</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>33570</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18584</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33790</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>14,81%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20280</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14459</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>28004</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35834</t>
+          <t>36505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57654</t>
+          <t>57332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>134521</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>127507</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>140663</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>145072</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>136718</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>151833</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>136498</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>151704</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>85,19%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>134521</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>126797</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>140342</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,9%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>267435</t>
+          <t>267757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>289255</t>
+          <t>288584</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>154801</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>154801</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>154801</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>170288</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>170288</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>170288</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>154801</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>154801</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>154801</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>86127</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>72231</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>100546</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,12%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>90719</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>75760</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>104758</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>78806</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>105613</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>86127</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>72588</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>100803</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157707</t>
+          <t>157190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198223</t>
+          <t>197258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>624274</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>609855</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>638170</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,88%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>859</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>574731</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>560692</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>589690</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>559837</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>586644</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>624274</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>609598</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>637813</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,88%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1177628</t>
+          <t>1178593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1218144</t>
+          <t>1218661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,58%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>710401</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>710401</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>710401</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>994</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>665450</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>665450</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>665450</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>710401</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>710401</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>710401</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8765</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5041</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14533</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9942</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5648</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15245</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5801</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15569</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,03%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8765</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4876</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14431</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25774</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>76799</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>71031</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80523</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,76%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>80178</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>74875</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>84472</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>74551</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>84319</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,97%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>76799</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>71133</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80688</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,76%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149910</t>
+          <t>148976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163148</t>
+          <t>162805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85564</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85564</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85564</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85564</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85564</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56122</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>45481</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68944</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>43136</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>33481</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>53467</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>33958</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>55361</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,85%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,21%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>56122</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>44143</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>67270</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84610</t>
+          <t>84179</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115926</t>
+          <t>116148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>418223</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>405401</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>428864</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,17%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>571</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>394864</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>384533</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>404519</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>382639</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>404042</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,15%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>418223</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>407075</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>430202</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,17%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>796418</t>
+          <t>796196</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>827734</t>
+          <t>828165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>474345</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>474345</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>474345</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>633</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>438000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>438000</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>438000</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>474345</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>474345</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>474345</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15220</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9635</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22517</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>19192</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13127</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26932</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12783</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26211</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,98%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15220</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9432</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22783</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26591</t>
+          <t>25714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45156</t>
+          <t>44194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>147582</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>140285</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>153167</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,17%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>140996</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>133256</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>147061</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>133977</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>147405</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,02%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>147582</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>140019</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>153370</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,65%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>277834</t>
+          <t>278796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>296399</t>
+          <t>297276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>162802</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>162802</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>162802</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>160188</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>160188</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>160188</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>162802</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>162802</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>162802</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>80108</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>67118</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>94708</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>72270</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>59395</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>86929</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>59649</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>86380</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>80108</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>66481</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>95393</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133597</t>
+          <t>135631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172759</t>
+          <t>172370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>642603</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>628003</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>655593</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>86,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>887</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>616037</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>601378</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>628912</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>601927</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>628658</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,5%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,37%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>917</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>642603</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>627318</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>656230</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,92%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1238259</t>
+          <t>1238648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1277421</t>
+          <t>1275387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>722711</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>722711</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>722711</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>991</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>688307</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>688307</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>688307</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>722711</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>722711</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>722711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9249</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5392</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14828</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8680</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4615</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14575</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4968</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14599</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>14,76%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9249</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5221</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15412</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26120</t>
+          <t>25289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59365</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>53786</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63222</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>86,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>50128</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44233</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54193</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>44209</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>53840</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>85,24%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59365</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>53202</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>63393</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>86,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101302</t>
+          <t>102133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115376</t>
+          <t>115083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68344</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>55627</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>81099</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,07%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>66877</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>55715</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>80244</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>54587</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>79728</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>14,41%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68344</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>56659</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>81588</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,07%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118694</t>
+          <t>118608</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153686</t>
+          <t>153941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>417451</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>404696</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>430168</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>83,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>601</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>397121</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>383754</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>408283</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>384270</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>409411</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>85,59%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>417451</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>404207</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>429136</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,93%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>796107</t>
+          <t>795852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>831099</t>
+          <t>831185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>485795</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>485795</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>485795</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>463998</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>463998</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>463998</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>485795</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>485795</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>485795</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29403</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21753</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>38525</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>25250</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18720</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34013</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18194</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33894</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>14,95%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>29403</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>21281</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>37882</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44567</t>
+          <t>43738</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66128</t>
+          <t>66309</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>152820</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>143698</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>160470</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>143610</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>134847</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>150140</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>134966</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>150666</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>85,05%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>152820</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>144341</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>160942</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,86%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284955</t>
+          <t>284774</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306516</t>
+          <t>307345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>168860</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>168860</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>168860</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>106996</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>90733</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>122750</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>100807</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>87132</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>116586</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>87884</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>117410</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>14,57%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>106996</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>91825</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>125082</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186417</t>
+          <t>186116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229676</t>
+          <t>232128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>629636</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>613882</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>645899</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>590860</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>575081</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>604535</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>574257</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>603783</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>85,43%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>629636</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>611550</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>644807</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,47%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1198623</t>
+          <t>1196171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1241882</t>
+          <t>1242183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>736632</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>736632</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>736632</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1040</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>691667</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>691667</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>691667</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>736632</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>736632</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>736632</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4621</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,08%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>375</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>384</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12001</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8604</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6012</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10552</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>80,92%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>56,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>18002</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22760</t>
+          <t>19300</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12001</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12001</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12001</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>10633</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10633</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10633</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>23345</t>
+          <t>19684</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23345</t>
+          <t>19684</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23345</t>
+          <t>19684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25493</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17054</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34445</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,88%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,03%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>19816</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13700</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>28340</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26341</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17935</t>
+          <t>11643</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35893</t>
+          <t>25457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>46156</t>
+          <t>43632</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36026</t>
+          <t>33215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59108</t>
+          <t>54180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>97395</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>88443</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>105834</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>79,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,12%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>67949</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>59425</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74065</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>77,42%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,39%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>106878</t>
+          <t>68566</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97326</t>
+          <t>61248</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>115284</t>
+          <t>75062</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>174828</t>
+          <t>165961</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161876</t>
+          <t>155413</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184958</t>
+          <t>176378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>84,15%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>87765</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>87765</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>87765</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>86705</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>86705</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>86705</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>220984</t>
+          <t>209593</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>220984</t>
+          <t>209593</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>220984</t>
+          <t>209593</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7793</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4429</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12743</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29,58%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12464</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8340</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17123</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>28,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>20484</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27516</t>
+          <t>27619</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35291</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30341</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>38655</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,91%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>70,42%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30784</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>26125</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>34908</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>71,18%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>60,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>80,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36975</t>
+          <t>30964</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32088</t>
+          <t>25738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40517</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>67760</t>
+          <t>66254</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60454</t>
+          <t>59119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73327</t>
+          <t>72357</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33286</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24706</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>42485</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>34308</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>26286</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>44143</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,56%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>32512</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25523</t>
+          <t>25021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45615</t>
+          <t>42385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>68395</t>
+          <t>65798</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56479</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83764</t>
+          <t>79361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>144687</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>135488</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>153267</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>107338</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>97503</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>115360</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>75,78%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>156566</t>
+          <t>105530</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145038</t>
+          <t>95657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165130</t>
+          <t>113021</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>263904</t>
+          <t>250217</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248535</t>
+          <t>236654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>275820</t>
+          <t>262197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177973</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177973</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177973</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>141646</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>141646</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>141646</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>190653</t>
+          <t>138042</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>190653</t>
+          <t>138042</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>190653</t>
+          <t>138042</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>332299</t>
+          <t>316015</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>332299</t>
+          <t>316015</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>332299</t>
+          <t>316015</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
